--- a/data/raw/fiscal/2021年天津市财力.xlsx
+++ b/data/raw/fiscal/2021年天津市财力.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\远东\4.业务发展\财力数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chen\Desktop\P3\agentic-credit-bd-assistant\data\raw\fiscal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{954080BC-2373-42C4-B524-984CDD14C56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FB0D99-61BA-4BD2-92E0-AD30D60BDB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{86984870-44B2-4489-96BA-9B3A1230BBB8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86984870-44B2-4489-96BA-9B3A1230BBB8}"/>
   </bookViews>
   <sheets>
     <sheet name="天津" sheetId="1" r:id="rId1"/>
@@ -51,52 +51,52 @@
     <t>天津市</t>
   </si>
   <si>
-    <t>浦东新区</t>
-  </si>
-  <si>
-    <t>黄浦区</t>
-  </si>
-  <si>
-    <t>闵行区</t>
-  </si>
-  <si>
-    <t>嘉定区</t>
-  </si>
-  <si>
-    <t>静安区</t>
-  </si>
-  <si>
-    <t>徐汇区</t>
-  </si>
-  <si>
-    <t>杨浦区</t>
-  </si>
-  <si>
-    <t>长宁区</t>
-  </si>
-  <si>
-    <t>松江区</t>
-  </si>
-  <si>
-    <t>宝山区</t>
-  </si>
-  <si>
-    <t>奉贤区</t>
-  </si>
-  <si>
-    <t>青浦区</t>
-  </si>
-  <si>
-    <t>普陀区</t>
-  </si>
-  <si>
-    <t>虹口区</t>
-  </si>
-  <si>
-    <t>金山区</t>
-  </si>
-  <si>
-    <t>崇明区</t>
+    <t>滨海新区</t>
+  </si>
+  <si>
+    <t>河西区</t>
+  </si>
+  <si>
+    <t>武清区</t>
+  </si>
+  <si>
+    <t>西青区</t>
+  </si>
+  <si>
+    <t>北辰区</t>
+  </si>
+  <si>
+    <t>南开区</t>
+  </si>
+  <si>
+    <t>和平区</t>
+  </si>
+  <si>
+    <t>东丽区</t>
+  </si>
+  <si>
+    <t>津南区</t>
+  </si>
+  <si>
+    <t>静海区</t>
+  </si>
+  <si>
+    <t>宝坻区</t>
+  </si>
+  <si>
+    <t>河东区</t>
+  </si>
+  <si>
+    <t>河北区</t>
+  </si>
+  <si>
+    <t>宁河区</t>
+  </si>
+  <si>
+    <t>蓟州区</t>
+  </si>
+  <si>
+    <t>红桥区</t>
   </si>
 </sst>
 </file>
@@ -462,9 +462,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFD67CF-9761-445D-9EAC-C97163A847EA}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -495,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1">
-        <v>15685.05</v>
+        <v>15695.05</v>
       </c>
       <c r="D2">
         <v>6.6</v>
@@ -510,372 +513,372 @@
         <v>3152.55</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="1">
-        <v>15352.99</v>
+        <v>6626.64</v>
       </c>
       <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1173.7</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1095.29</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1288.49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>7.3</v>
+      </c>
+      <c r="E3">
+        <v>572.41</v>
+      </c>
+      <c r="F3">
+        <v>505.68</v>
+      </c>
+      <c r="G3">
+        <v>807.91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1">
-        <v>2902.4</v>
+        <v>1088.31</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="E4">
-        <v>267.02999999999997</v>
+        <v>55.81</v>
       </c>
       <c r="F4">
-        <v>241.02</v>
+        <v>48.81</v>
       </c>
       <c r="G4">
-        <v>322.68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+        <v>79.39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1">
-        <v>2843.19</v>
+      <c r="C5">
+        <v>929.76</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="E5">
-        <v>331.1</v>
+        <v>95.33</v>
       </c>
       <c r="F5">
-        <v>300</v>
+        <v>72.680000000000007</v>
       </c>
       <c r="G5">
-        <v>402.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+        <v>144.32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1">
-        <v>2705.6</v>
+      <c r="C6">
+        <v>927.03</v>
       </c>
       <c r="D6">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="E6">
-        <v>243.51</v>
+        <v>69.41</v>
       </c>
       <c r="F6">
-        <v>224.74</v>
+        <v>53.92</v>
       </c>
       <c r="G6">
-        <v>336.38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+        <v>103.61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1">
-        <v>2565.4299999999998</v>
+      <c r="C7">
+        <v>695.77</v>
       </c>
       <c r="D7">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E7">
-        <v>278.48</v>
+        <v>59.46</v>
       </c>
       <c r="F7">
-        <v>247.59</v>
+        <v>41.84</v>
       </c>
       <c r="G7">
-        <v>292.70999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <v>83.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1">
-        <v>2438.48</v>
+      <c r="C8">
+        <v>694.54</v>
       </c>
       <c r="D8">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="E8">
-        <v>220.54</v>
+        <v>39.65</v>
       </c>
       <c r="F8">
-        <v>199.64</v>
+        <v>32.119999999999997</v>
       </c>
       <c r="G8">
-        <v>320.92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <v>56.79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1">
-        <v>1951.32</v>
+      <c r="C9">
+        <v>682.88</v>
       </c>
       <c r="D9">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E9">
-        <v>143.01</v>
+        <v>37.78</v>
       </c>
       <c r="F9">
-        <v>111.57</v>
+        <v>32.26</v>
       </c>
       <c r="G9">
-        <v>205.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+        <v>52.47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1">
-        <v>1826.52</v>
+      <c r="C10">
+        <v>664.71</v>
       </c>
       <c r="D10">
-        <v>11.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E10">
-        <v>150.33000000000001</v>
+        <v>58.57</v>
       </c>
       <c r="F10">
-        <v>135.06</v>
+        <v>41.8</v>
       </c>
       <c r="G10">
-        <v>143.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+        <v>79.040000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="1">
-        <v>1782.28</v>
+      <c r="C11">
+        <v>583.29</v>
       </c>
       <c r="D11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="E11">
-        <v>250.1</v>
+        <v>61.53</v>
       </c>
       <c r="F11">
-        <v>200.75</v>
+        <v>41.15</v>
       </c>
       <c r="G11">
-        <v>354.68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+        <v>157.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1">
-        <v>1725.56</v>
+      <c r="C12">
+        <v>477.16</v>
       </c>
       <c r="D12">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="E12">
-        <v>172.9</v>
+        <v>48.61</v>
       </c>
       <c r="F12">
-        <v>146.26</v>
+        <v>30.52</v>
       </c>
       <c r="G12">
-        <v>278.45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <v>83.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="1">
-        <v>1330.09</v>
+      <c r="C13">
+        <v>435.16</v>
       </c>
       <c r="D13">
-        <v>9.3000000000000007</v>
+        <v>7.1</v>
       </c>
       <c r="E13">
-        <v>220.8</v>
+        <v>31.74</v>
       </c>
       <c r="F13">
-        <v>194.4</v>
+        <v>22.18</v>
       </c>
       <c r="G13">
-        <v>332.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <v>90.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="1">
-        <v>1317.25</v>
+      <c r="C14">
+        <v>431.02</v>
       </c>
       <c r="D14">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="E14">
-        <v>231.1</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="F14">
-        <v>192.64</v>
+        <v>29.55</v>
       </c>
       <c r="G14">
-        <v>354.97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+        <v>60.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="1">
-        <v>1226.49</v>
+      <c r="C15">
+        <v>366.38</v>
       </c>
       <c r="D15">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="E15">
-        <v>125.56</v>
+        <v>21.35</v>
       </c>
       <c r="F15">
-        <v>107.65</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="G15">
-        <v>176.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+        <v>42.91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="1">
-        <v>1214.77</v>
+      <c r="C16">
+        <v>337.55</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="E16">
-        <v>155.22999999999999</v>
+        <v>23.06</v>
       </c>
       <c r="F16">
-        <v>139.77000000000001</v>
+        <v>18.04</v>
       </c>
       <c r="G16">
-        <v>195.02</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+        <v>54.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="1">
-        <v>1182.78</v>
+      <c r="C17">
+        <v>274.2</v>
       </c>
       <c r="D17">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>134.32</v>
+        <v>22.52</v>
       </c>
       <c r="F17">
-        <v>119.65</v>
+        <v>12.35</v>
       </c>
       <c r="G17">
-        <v>243.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+        <v>115.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18">
-        <v>409.72</v>
+        <v>176.93</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E18">
-        <v>146.05000000000001</v>
+        <v>19.23</v>
       </c>
       <c r="F18">
-        <v>138.30000000000001</v>
+        <v>11.48</v>
       </c>
       <c r="G18">
-        <v>338.82</v>
+        <v>41.94</v>
       </c>
     </row>
   </sheetData>
